--- a/TAZA/_документы/Бюджет ЦАКФ.xlsx
+++ b/TAZA/_документы/Бюджет ЦАКФ.xlsx
@@ -1177,9 +1177,6 @@
     <t xml:space="preserve">  в т.ч. Фонд</t>
   </si>
   <si>
-    <t>[Қаражан Е.Н.] Общее руководство Фондом и проектным офисом, соглашение с МЭПР, отчётность перед органами Фонда. Опыт: к.э.н. (PhD), MSc LSE («Болашақ»), Chevening; ГИД ЦАКФ с 02.2025 (Региональный экологический саммит 2026); председатель Правления ИЭИ, советник Министра национальной экономики, консультант АБР, директор по устойчивому развитию ФНБ «Самрук-Қазына».</t>
-  </si>
-  <si>
     <t>[Тленчиева Ш.] Исследования восприятия акции, опросы. Опыт: PhD по социологии.</t>
   </si>
   <si>
@@ -1333,21 +1330,12 @@
     <t>[Темирбеков М.Е.] Наём, закупки, офис, договоры с поставщиками. Опыт: международные экономические отношения (диплом с отличием); акиматы Костанайской области и Астаны; руководитель аппарата холдинга (3 000+ сотрудников); проекты МЗ РК и Всемирного банка; руководитель в общественных организациях, структур в квазигоссекторе; в ЦАКФ с 02.2025, член Управляющего совета.</t>
   </si>
   <si>
-    <t>Заместитель ГИД по стратегии и проектам</t>
-  </si>
-  <si>
     <t>Проектный офис для Центральной Азии по изменению климата и зеленой энергетике</t>
   </si>
   <si>
     <t>Менеджер проектов</t>
   </si>
   <si>
-    <t>Руководителю Проектного офиса для Центральной Азии</t>
-  </si>
-  <si>
-    <t>[Кононец А.В.] Стратегия и портфель проектов Фонда, партнёрства; Проектный офис для Центральной Азии; курация проектного управления. Опыт: 20 лет в медиа и госкоммуникациях – руководитель пресс-службы, советник министра труда и социальной защиты, главный редактор Казправды, Total.kz и др.; в ЦАКФ с 07.2025.</t>
-  </si>
-  <si>
     <t>Руководитель проектного офиса «Таза Қазақстан»</t>
   </si>
   <si>
@@ -1373,6 +1361,18 @@
   </si>
   <si>
     <t>Штатная структура ЦАКФ по штатному расписанию 01.10.2026 и расходы на персонал, ₸</t>
+  </si>
+  <si>
+    <t>Советник ГИД по стратегии и науке</t>
+  </si>
+  <si>
+    <t>[Кононец А.В.] Стратегия и научное направление Фонда, аналитические и экспертные материалы, международные партнёры; поручения ГИД. Опыт: 20 лет в медиа и госкоммуникациях – руководитель пресс-службы, советник министра труда и социальной защиты, главный редактор Казправды, Total.kz и др.; в ЦАКФ с 07.2025.</t>
+  </si>
+  <si>
+    <t>[Қаражан Е.Н.] Общее руководство Фондом и проектным офисом, руководство Проектным офисом для Центральной Азии, соглашение с МЭПР, отчётность перед органами Фонда. Опыт: к.э.н. (PhD), MSc LSE («Болашақ»), Chevening; ГИД ЦАКФ с 02.2025 (Региональный экологический саммит 2026); председатель Правления ИЭИ, советник Министра национальной экономики, консультант АБР, директор по устойчивому развитию ФНБ «Самрук-Қазына».</t>
+  </si>
+  <si>
+    <t>ГИД (Руководитель Проектного офиса для Центральной Азии)</t>
   </si>
 </sst>
 </file>
@@ -1875,7 +1875,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="33" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1888,7 +1888,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="36" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B4" s="37">
         <f>SUMIF(Штат!E5:E29,"штат",Штат!G5:G29)</f>
@@ -1897,7 +1897,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="36" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B5" s="37">
         <f>Штат!G31</f>
@@ -1906,7 +1906,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="36" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B6" s="38">
         <f>SUMIFS(Штат!M5:M29,Штат!E5:E29,"штат")</f>
@@ -1915,7 +1915,7 @@
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="36" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B7" s="38">
         <f>Аутсорс!J11</f>
@@ -1924,7 +1924,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="36" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B8" s="38">
         <f>Штат!N30</f>
@@ -1933,7 +1933,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="36" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B9" s="38">
         <f>Командировки!G12</f>
@@ -1942,7 +1942,7 @@
     </row>
     <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="36" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B10" s="38">
         <f>SUMIFS('Оснащение и офис'!I5:I57,'Оснащение и офис'!A5:A57,"Оснащение")</f>
@@ -1951,7 +1951,7 @@
     </row>
     <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="36" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B11" s="38">
         <f>SUMIFS('Оснащение и офис'!I5:I57,'Оснащение и офис'!A5:A57,"Офис")</f>
@@ -1960,7 +1960,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="36" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B12" s="38">
         <f>SUMIFS('Оснащение и офис'!I5:I57,'Оснащение и офис'!A5:A57,"Цифровые")</f>
@@ -1969,7 +1969,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="36" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B13" s="38">
         <f>SUMIFS('Оснащение и офис'!I5:I57,'Оснащение и офис'!A5:A57,"Медиа")</f>
@@ -1978,7 +1978,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="39" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B14" s="40">
         <f>B6+B7+B8+B9+B10+B11+B12+B13</f>
@@ -1987,7 +1987,7 @@
     </row>
     <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="36" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B15" s="38">
         <f>B14*Резерв+SUMIFS('Оснащение и офис'!I5:I57,'Оснащение и офис'!A5:A57,"Прочие")</f>
@@ -2005,7 +2005,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="41" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B17" s="42">
         <f>B14+B15+B16</f>
@@ -2014,7 +2014,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="39" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B18" s="40">
         <f>Проекты!G13</f>
@@ -2023,7 +2023,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="43" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B19" s="44">
         <f>B17+B18</f>
@@ -2188,13 +2188,13 @@
     </row>
     <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B15" s="8">
         <v>500000</v>
       </c>
       <c r="C15" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2423,12 +2423,12 @@
     </row>
     <row r="37" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="41" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -2554,7 +2554,7 @@
         <v>2.3548387096774195</v>
       </c>
       <c r="C52" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
   </sheetData>
@@ -2582,7 +2582,7 @@
   <sheetData>
     <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2629,7 +2629,7 @@
         <v>77</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O4" s="3" t="s">
         <v>78</v>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="Q4" s="4"/>
     </row>
-    <row r="5" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A5" s="16">
         <v>1</v>
       </c>
@@ -2692,7 +2692,7 @@
         <v>5454690</v>
       </c>
       <c r="P5" s="17" t="s">
-        <v>351</v>
+        <v>415</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="60" x14ac:dyDescent="0.25">
@@ -2703,7 +2703,7 @@
         <v>281</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="D6" s="17" t="s">
         <v>82</v>
@@ -2748,7 +2748,7 @@
         <v>4784010</v>
       </c>
       <c r="P6" s="17" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="90" x14ac:dyDescent="0.25">
@@ -2804,7 +2804,7 @@
         <v>4784010</v>
       </c>
       <c r="P7" s="17" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="90" x14ac:dyDescent="0.25">
@@ -2815,7 +2815,7 @@
         <v>215</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D8" s="17" t="s">
         <v>82</v>
@@ -2860,7 +2860,7 @@
         <v>3790904.9308755766</v>
       </c>
       <c r="P8" s="17" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="30" x14ac:dyDescent="0.25">
@@ -2916,7 +2916,7 @@
         <v>2738009.4470046088</v>
       </c>
       <c r="P9" s="17" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="30" x14ac:dyDescent="0.25">
@@ -3028,7 +3028,7 @@
         <v>2738009.4470046088</v>
       </c>
       <c r="P11" s="17" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="75" x14ac:dyDescent="0.25">
@@ -3084,7 +3084,7 @@
         <v>2738009.4470046088</v>
       </c>
       <c r="P12" s="17" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="60" x14ac:dyDescent="0.25">
@@ -3140,7 +3140,7 @@
         <v>2738009.4470046088</v>
       </c>
       <c r="P13" s="17" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="75" x14ac:dyDescent="0.25">
@@ -3196,7 +3196,7 @@
         <v>1948337.8341013826</v>
       </c>
       <c r="P14" s="17" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="75" x14ac:dyDescent="0.25">
@@ -3252,7 +3252,7 @@
         <v>3527681.0599078345</v>
       </c>
       <c r="P15" s="17" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="30" x14ac:dyDescent="0.25">
@@ -3364,7 +3364,7 @@
         <v>3527681.0599078345</v>
       </c>
       <c r="P17" s="17" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="18" spans="1:16" ht="45" x14ac:dyDescent="0.25">
@@ -3420,7 +3420,7 @@
         <v>2738009.4470046088</v>
       </c>
       <c r="P18" s="17" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
@@ -3812,7 +3812,7 @@
         <v>4784010</v>
       </c>
       <c r="P25" s="17" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="26" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -3876,13 +3876,13 @@
         <v>35</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="E27" s="16" t="s">
         <v>80</v>
@@ -3924,7 +3924,7 @@
         <v>3264457.1889400925</v>
       </c>
       <c r="P27" s="17" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="28" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -4129,7 +4129,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
@@ -4521,7 +4521,7 @@
     <row r="6" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="str">
         <f>Штат!C6</f>
-        <v>Заместитель ГИД по стратегии и проектам</v>
+        <v>Советник ГИД по стратегии и науке</v>
       </c>
       <c r="C6">
         <f>Штат!G6</f>
@@ -4697,12 +4697,12 @@
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4725,7 +4725,7 @@
         <v>96</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>97</v>
@@ -4757,7 +4757,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="I5" s="5">
         <f t="shared" ref="I5:I39" si="0">IF(F5="разово",IF(G5&lt;=3,D5*E5,0),IF(F5="мес",D5*E5*MAX(0,4-G5),D5*E5*MAX(0,4-G5)/12))</f>
@@ -4917,7 +4917,7 @@
         <v>98</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C11" t="s">
         <v>104</v>
@@ -5327,7 +5327,7 @@
         <v>1</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="I24" s="5">
         <f t="shared" si="0"/>
@@ -5358,7 +5358,7 @@
         <v>1</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="I25" s="5">
         <f t="shared" si="0"/>
@@ -5613,7 +5613,7 @@
         <v>98</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C34" t="s">
         <v>115</v>
@@ -5632,7 +5632,7 @@
         <v>1</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="I34" s="5">
         <f t="shared" si="0"/>
@@ -5759,7 +5759,7 @@
         <v>98</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C39" t="s">
         <v>100</v>
@@ -5961,7 +5961,7 @@
         <v>118</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C46" t="s">
         <v>120</v>
@@ -5980,7 +5980,7 @@
         <v>1</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="I46" s="5">
         <f t="shared" si="3"/>
@@ -5992,7 +5992,7 @@
         <v>118</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C47" t="s">
         <v>104</v>
@@ -6011,7 +6011,7 @@
         <v>1</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="I47" s="5">
         <f t="shared" ref="I47" si="4">IF(F47="разово",IF(G47&lt;=3,D47*E47,0),IF(F47="мес",D47*E47*MAX(0,4-G47),D47*E47*MAX(0,4-G47)/12))</f>
@@ -6069,7 +6069,7 @@
         <v>1</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="I49" s="5">
         <f t="shared" si="3"/>
@@ -6244,7 +6244,7 @@
         <v>140</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C56" t="s">
         <v>104</v>
@@ -6272,7 +6272,7 @@
         <v>140</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C57" t="s">
         <v>138</v>
@@ -6321,7 +6321,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -6488,7 +6488,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B13" s="7" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -6524,7 +6524,7 @@
   <sheetData>
     <row r="1" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -6707,7 +6707,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
@@ -6864,7 +6864,7 @@
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="7"/>
       <c r="B20" s="7" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C20" s="7"/>
       <c r="D20" s="32"/>
@@ -7130,7 +7130,7 @@
     </row>
     <row r="15" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
